--- a/artfynd/A 55860-2024 artfynd.xlsx
+++ b/artfynd/A 55860-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AZ106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539912</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119194216</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539893</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539899</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539916</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181443</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539877</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1691,6 +1736,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539878</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539887</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1921,6 +1976,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539892</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2036,6 +2096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539898</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2151,6 +2216,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539900</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2266,6 +2336,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539906</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2381,6 +2456,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539909</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2496,6 +2576,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539918</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2611,6 +2696,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539924</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2726,6 +2816,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539936</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2841,6 +2936,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539937</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2956,6 +3056,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539938</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3071,6 +3176,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539946</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3186,6 +3296,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539970</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3301,6 +3416,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539992</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3416,6 +3536,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539917</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3531,6 +3656,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539932</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3646,6 +3776,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539989</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3753,6 +3888,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180250</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3868,6 +4008,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539882</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3983,6 +4128,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539894</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4098,6 +4248,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539895</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4213,6 +4368,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539905</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4328,6 +4488,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539985</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4444,6 +4609,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539910</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4559,6 +4729,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539889</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4674,6 +4849,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539907</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4781,6 +4961,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119194249</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4878,6 +5063,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230353</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4975,6 +5165,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119238545</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5090,6 +5285,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539876</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5205,6 +5405,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539885</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5320,6 +5525,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539888</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5430,6 +5640,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539903</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5540,6 +5755,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539908</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5650,6 +5870,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539926</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5760,6 +5985,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539929</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5875,6 +6105,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539879</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5990,6 +6225,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539891</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6105,6 +6345,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539904</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6220,6 +6465,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539930</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6335,6 +6585,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539928</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6442,6 +6697,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180649</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6549,6 +6809,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180677</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6656,6 +6921,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181399</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6753,6 +7023,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119238497</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6868,6 +7143,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539884</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6975,6 +7255,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181367</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7072,6 +7357,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230318</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7169,6 +7459,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230465</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7279,6 +7574,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539890</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7389,6 +7689,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539921</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7496,6 +7801,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180308</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7603,6 +7913,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180615</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7710,6 +8025,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119193879</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7817,6 +8137,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119194273</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7914,6 +8239,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230266</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8011,6 +8341,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230667</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8118,6 +8453,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180746</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8225,6 +8565,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181427</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8322,6 +8667,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230344</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8419,6 +8769,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119224894</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8529,6 +8884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539919</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8644,6 +9004,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539953</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8751,6 +9116,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180935</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8858,6 +9228,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180402</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8973,6 +9348,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539934</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9070,6 +9450,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230451</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9185,6 +9570,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539914</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9300,6 +9690,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539931</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9407,6 +9802,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180779</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9523,6 +9923,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180329</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9630,6 +10035,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181114</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9746,6 +10156,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181007</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9862,6 +10277,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181034</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9978,6 +10398,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181118</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10094,6 +10519,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181149</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10204,6 +10634,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539915</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10314,6 +10749,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539920</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10421,6 +10861,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181131</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10528,6 +10973,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180394</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10635,6 +11085,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119180502</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10742,6 +11197,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181344</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10839,6 +11299,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230278</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10936,6 +11401,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119230444</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11047,6 +11517,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539880</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11162,6 +11637,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539896</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11277,6 +11757,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539913</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11392,6 +11877,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539925</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11507,6 +11997,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539945</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11622,6 +12117,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539972</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11737,6 +12237,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539988</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11844,6 +12349,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119181423</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11959,6 +12469,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539886</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12074,6 +12589,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539901</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12189,6 +12709,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539927</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12304,8 +12829,120 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119539911</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>